--- a/Datasets/References_audios_bb.xlsx
+++ b/Datasets/References_audios_bb.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Margherita\Desktop\SOA_Projet\paper1\currbio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Margherita\Documents\GitHub\SOABB1\Datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A01FD8-D297-4BC0-9226-1D325D56065A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6855B63B-5951-4A35-813D-605B1786B6B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="details" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">details!$A$1:$O$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">details!$A$1:$L$164</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="96">
   <si>
     <t>BB</t>
   </si>
@@ -69,18 +69,9 @@
     <t>Type_modif</t>
   </si>
   <si>
-    <t>Ordre_babylab</t>
-  </si>
-  <si>
     <t>Ordre_miroir</t>
   </si>
   <si>
-    <t>deja_venu</t>
-  </si>
-  <si>
-    <t>code_3m</t>
-  </si>
-  <si>
     <t>Mirror_recognition</t>
   </si>
   <si>
@@ -222,30 +213,15 @@
     <t>1m43</t>
   </si>
   <si>
-    <t>88 excl</t>
-  </si>
-  <si>
-    <t>55 excl</t>
-  </si>
-  <si>
     <t>6m28</t>
   </si>
   <si>
-    <t>?</t>
-  </si>
-  <si>
-    <t>67 excl</t>
-  </si>
-  <si>
     <t>1m25</t>
   </si>
   <si>
     <t>3m40</t>
   </si>
   <si>
-    <t>89 excl</t>
-  </si>
-  <si>
     <t>1m15</t>
   </si>
   <si>
@@ -292,9 +268,6 @@
   </si>
   <si>
     <t>04m30</t>
-  </si>
-  <si>
-    <t>BB102 EXCLU</t>
   </si>
   <si>
     <t>3m14</t>
@@ -686,7 +659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T997"/>
+  <dimension ref="A1:Q997"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.796875" style="1" customWidth="1"/>
@@ -699,15 +672,12 @@
     <col min="8" max="8" width="12.59765625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.8984375" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.8984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.5" style="2" customWidth="1"/>
-    <col min="16" max="20" width="10.5" style="2" customWidth="1"/>
+    <col min="11" max="11" width="12.296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.5" style="2" customWidth="1"/>
+    <col min="13" max="17" width="10.5" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -744,22 +714,13 @@
       <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
       <c r="P1" s="5"/>
       <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-    </row>
-    <row r="2" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -776,10 +737,10 @@
         <v>6</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I2" s="5">
         <v>79</v>
@@ -787,22 +748,15 @@
       <c r="J2" s="5">
         <v>100</v>
       </c>
-      <c r="K2" s="5">
-        <v>2</v>
-      </c>
+      <c r="K2" s="5"/>
       <c r="L2" s="5"/>
-      <c r="M2" s="5">
-        <v>0</v>
-      </c>
+      <c r="M2" s="5"/>
       <c r="N2" s="5"/>
       <c r="O2" s="5"/>
       <c r="P2" s="5"/>
       <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-    </row>
-    <row r="3" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -818,29 +772,22 @@
         <v>9</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5">
         <v>-100</v>
       </c>
-      <c r="K3" s="5">
-        <v>2</v>
-      </c>
+      <c r="K3" s="5"/>
       <c r="L3" s="5"/>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
+      <c r="M3" s="5"/>
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-    </row>
-    <row r="4" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -856,29 +803,22 @@
         <v>9</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="5">
         <v>100</v>
       </c>
-      <c r="K4" s="5">
-        <v>2</v>
-      </c>
+      <c r="K4" s="5"/>
       <c r="L4" s="5"/>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
+      <c r="M4" s="5"/>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
       <c r="P4" s="5"/>
       <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
-      <c r="S4" s="5"/>
-      <c r="T4" s="5"/>
-    </row>
-    <row r="5" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -894,29 +834,22 @@
         <v>6</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
       <c r="J5" s="5">
         <v>-100</v>
       </c>
-      <c r="K5" s="5">
-        <v>2</v>
-      </c>
+      <c r="K5" s="5"/>
       <c r="L5" s="5"/>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
+      <c r="M5" s="5"/>
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
-      <c r="R5" s="5"/>
-      <c r="S5" s="5"/>
-      <c r="T5" s="5"/>
-    </row>
-    <row r="6" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -932,29 +865,22 @@
         <v>6</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
       <c r="J6" s="5">
         <v>100</v>
       </c>
-      <c r="K6" s="5">
-        <v>2</v>
-      </c>
+      <c r="K6" s="5"/>
       <c r="L6" s="5"/>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
+      <c r="M6" s="5"/>
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
-      <c r="S6" s="5"/>
-      <c r="T6" s="5"/>
-    </row>
-    <row r="7" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -970,29 +896,22 @@
         <v>6</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
       <c r="J7" s="5">
         <v>-100</v>
       </c>
-      <c r="K7" s="5">
-        <v>2</v>
-      </c>
+      <c r="K7" s="5"/>
       <c r="L7" s="5"/>
-      <c r="M7" s="5">
-        <v>0</v>
-      </c>
+      <c r="M7" s="5"/>
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
-      <c r="R7" s="5"/>
-      <c r="S7" s="5"/>
-      <c r="T7" s="5"/>
-    </row>
-    <row r="8" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -1009,10 +928,10 @@
         <v>6</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I8" s="5">
         <v>80</v>
@@ -1020,16 +939,9 @@
       <c r="J8" s="5">
         <v>100</v>
       </c>
-      <c r="K8" s="5">
-        <v>2</v>
-      </c>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5">
-        <v>0</v>
-      </c>
-      <c r="N8" s="5"/>
-    </row>
-    <row r="9" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K8" s="5"/>
+    </row>
+    <row r="9" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -1045,29 +957,22 @@
         <v>9</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
       <c r="J9" s="5">
         <v>-100</v>
       </c>
-      <c r="K9" s="5">
-        <v>2</v>
-      </c>
+      <c r="K9" s="5"/>
       <c r="L9" s="5"/>
-      <c r="M9" s="5">
-        <v>0</v>
-      </c>
+      <c r="M9" s="5"/>
       <c r="N9" s="5"/>
       <c r="O9" s="5"/>
       <c r="P9" s="5"/>
       <c r="Q9" s="5"/>
-      <c r="R9" s="5"/>
-      <c r="S9" s="5"/>
-      <c r="T9" s="5"/>
-    </row>
-    <row r="10" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -1083,29 +988,22 @@
         <v>6</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
       <c r="J10" s="5">
         <v>-100</v>
       </c>
-      <c r="K10" s="5">
-        <v>2</v>
-      </c>
+      <c r="K10" s="5"/>
       <c r="L10" s="5"/>
-      <c r="M10" s="5">
-        <v>0</v>
-      </c>
+      <c r="M10" s="5"/>
       <c r="N10" s="5"/>
       <c r="O10" s="5"/>
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
-      <c r="R10" s="5"/>
-      <c r="S10" s="5"/>
-      <c r="T10" s="5"/>
-    </row>
-    <row r="11" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -1121,10 +1019,10 @@
         <v>9</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I11" s="5">
         <v>139</v>
@@ -1132,22 +1030,15 @@
       <c r="J11" s="5">
         <v>-100</v>
       </c>
-      <c r="K11" s="5">
-        <v>2</v>
-      </c>
+      <c r="K11" s="5"/>
       <c r="L11" s="5"/>
-      <c r="M11" s="5">
-        <v>0</v>
-      </c>
+      <c r="M11" s="5"/>
       <c r="N11" s="5"/>
       <c r="O11" s="5"/>
       <c r="P11" s="5"/>
       <c r="Q11" s="5"/>
-      <c r="R11" s="5"/>
-      <c r="S11" s="5"/>
-      <c r="T11" s="5"/>
-    </row>
-    <row r="12" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -1163,29 +1054,22 @@
         <v>3</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
       <c r="J12" s="5">
         <v>-100</v>
       </c>
-      <c r="K12" s="5">
-        <v>2</v>
-      </c>
+      <c r="K12" s="5"/>
       <c r="L12" s="5"/>
-      <c r="M12" s="5">
-        <v>0</v>
-      </c>
+      <c r="M12" s="5"/>
       <c r="N12" s="5"/>
       <c r="O12" s="5"/>
       <c r="P12" s="5"/>
       <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
-      <c r="S12" s="5"/>
-      <c r="T12" s="5"/>
-    </row>
-    <row r="13" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -1202,10 +1086,10 @@
         <v>6</v>
       </c>
       <c r="G13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="5" t="s">
         <v>17</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>20</v>
       </c>
       <c r="I13" s="5">
         <v>173</v>
@@ -1213,22 +1097,15 @@
       <c r="J13" s="5">
         <v>-100</v>
       </c>
-      <c r="K13" s="5">
-        <v>2</v>
-      </c>
+      <c r="K13" s="5"/>
       <c r="L13" s="5"/>
-      <c r="M13" s="5">
-        <v>0</v>
-      </c>
+      <c r="M13" s="5"/>
       <c r="N13" s="5"/>
       <c r="O13" s="5"/>
       <c r="P13" s="5"/>
       <c r="Q13" s="5"/>
-      <c r="R13" s="5"/>
-      <c r="S13" s="5"/>
-      <c r="T13" s="5"/>
-    </row>
-    <row r="14" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -1244,29 +1121,22 @@
         <v>6</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
       <c r="J14" s="5">
         <v>100</v>
       </c>
-      <c r="K14" s="5">
-        <v>2</v>
-      </c>
+      <c r="K14" s="5"/>
       <c r="L14" s="5"/>
-      <c r="M14" s="5">
-        <v>0</v>
-      </c>
+      <c r="M14" s="5"/>
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
       <c r="P14" s="5"/>
       <c r="Q14" s="5"/>
-      <c r="R14" s="5"/>
-      <c r="S14" s="5"/>
-      <c r="T14" s="5"/>
-    </row>
-    <row r="15" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -1282,29 +1152,22 @@
         <v>6</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="5">
         <v>100</v>
       </c>
-      <c r="K15" s="5">
-        <v>2</v>
-      </c>
+      <c r="K15" s="5"/>
       <c r="L15" s="5"/>
-      <c r="M15" s="5">
-        <v>0</v>
-      </c>
+      <c r="M15" s="5"/>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
       <c r="P15" s="5"/>
       <c r="Q15" s="5"/>
-      <c r="R15" s="5"/>
-      <c r="S15" s="5"/>
-      <c r="T15" s="5"/>
-    </row>
-    <row r="16" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -1321,10 +1184,10 @@
         <v>6</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I16" s="5">
         <v>640</v>
@@ -1332,22 +1195,15 @@
       <c r="J16" s="5">
         <v>100</v>
       </c>
-      <c r="K16" s="5">
-        <v>1</v>
-      </c>
+      <c r="K16" s="5"/>
       <c r="L16" s="5"/>
-      <c r="M16" s="5">
-        <v>0</v>
-      </c>
+      <c r="M16" s="5"/>
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
       <c r="P16" s="5"/>
       <c r="Q16" s="5"/>
-      <c r="R16" s="5"/>
-      <c r="S16" s="5"/>
-      <c r="T16" s="5"/>
-    </row>
-    <row r="17" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -1363,10 +1219,10 @@
         <v>9</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I17" s="5">
         <v>288</v>
@@ -1374,22 +1230,15 @@
       <c r="J17" s="5">
         <v>100</v>
       </c>
-      <c r="K17" s="5">
-        <v>1</v>
-      </c>
+      <c r="K17" s="5"/>
       <c r="L17" s="5"/>
-      <c r="M17" s="5">
-        <v>0</v>
-      </c>
+      <c r="M17" s="5"/>
       <c r="N17" s="5"/>
       <c r="O17" s="5"/>
       <c r="P17" s="5"/>
       <c r="Q17" s="5"/>
-      <c r="R17" s="5"/>
-      <c r="S17" s="5"/>
-      <c r="T17" s="5"/>
-    </row>
-    <row r="18" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -1405,29 +1254,22 @@
         <v>9</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
       <c r="J18" s="5">
         <v>-100</v>
       </c>
-      <c r="K18" s="5">
-        <v>1</v>
-      </c>
+      <c r="K18" s="5"/>
       <c r="L18" s="5"/>
-      <c r="M18" s="5">
-        <v>0</v>
-      </c>
+      <c r="M18" s="5"/>
       <c r="N18" s="5"/>
       <c r="O18" s="5"/>
       <c r="P18" s="5"/>
       <c r="Q18" s="5"/>
-      <c r="R18" s="5"/>
-      <c r="S18" s="5"/>
-      <c r="T18" s="5"/>
-    </row>
-    <row r="19" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -1444,10 +1286,10 @@
         <v>6</v>
       </c>
       <c r="G19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="5" t="s">
         <v>15</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>18</v>
       </c>
       <c r="I19" s="5">
         <v>80</v>
@@ -1455,22 +1297,15 @@
       <c r="J19" s="5">
         <v>-100</v>
       </c>
-      <c r="K19" s="5">
-        <v>1</v>
-      </c>
+      <c r="K19" s="5"/>
       <c r="L19" s="5"/>
-      <c r="M19" s="5">
-        <v>0</v>
-      </c>
+      <c r="M19" s="5"/>
       <c r="N19" s="5"/>
       <c r="O19" s="5"/>
       <c r="P19" s="5"/>
       <c r="Q19" s="5"/>
-      <c r="R19" s="5"/>
-      <c r="S19" s="5"/>
-      <c r="T19" s="5"/>
-    </row>
-    <row r="20" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -1486,10 +1321,10 @@
         <v>9</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I20" s="5">
         <v>76</v>
@@ -1497,22 +1332,15 @@
       <c r="J20" s="5">
         <v>100</v>
       </c>
-      <c r="K20" s="5">
-        <v>2</v>
-      </c>
+      <c r="K20" s="5"/>
       <c r="L20" s="5"/>
-      <c r="M20" s="5">
-        <v>0</v>
-      </c>
+      <c r="M20" s="5"/>
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>
       <c r="P20" s="5"/>
       <c r="Q20" s="5"/>
-      <c r="R20" s="5"/>
-      <c r="S20" s="5"/>
-      <c r="T20" s="5"/>
-    </row>
-    <row r="21" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -1528,10 +1356,10 @@
         <v>9</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I21" s="5">
         <v>330</v>
@@ -1539,22 +1367,15 @@
       <c r="J21" s="5">
         <v>-100</v>
       </c>
-      <c r="K21" s="5">
-        <v>2</v>
-      </c>
+      <c r="K21" s="5"/>
       <c r="L21" s="5"/>
-      <c r="M21" s="5">
-        <v>0</v>
-      </c>
+      <c r="M21" s="5"/>
       <c r="N21" s="5"/>
       <c r="O21" s="5"/>
       <c r="P21" s="5"/>
       <c r="Q21" s="5"/>
-      <c r="R21" s="5"/>
-      <c r="S21" s="5"/>
-      <c r="T21" s="5"/>
-    </row>
-    <row r="22" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -1571,10 +1392,10 @@
         <v>6</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I22" s="5">
         <v>255</v>
@@ -1582,22 +1403,15 @@
       <c r="J22" s="5">
         <v>-100</v>
       </c>
-      <c r="K22" s="5">
-        <v>2</v>
-      </c>
+      <c r="K22" s="5"/>
       <c r="L22" s="5"/>
-      <c r="M22" s="5">
-        <v>0</v>
-      </c>
+      <c r="M22" s="5"/>
       <c r="N22" s="5"/>
       <c r="O22" s="5"/>
       <c r="P22" s="5"/>
       <c r="Q22" s="5"/>
-      <c r="R22" s="5"/>
-      <c r="S22" s="5"/>
-      <c r="T22" s="5"/>
-    </row>
-    <row r="23" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -1613,10 +1427,10 @@
         <v>9</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I23" s="5">
         <v>287</v>
@@ -1624,22 +1438,15 @@
       <c r="J23" s="5">
         <v>-100</v>
       </c>
-      <c r="K23" s="5">
-        <v>2</v>
-      </c>
+      <c r="K23" s="5"/>
       <c r="L23" s="5"/>
-      <c r="M23" s="5">
-        <v>0</v>
-      </c>
+      <c r="M23" s="5"/>
       <c r="N23" s="5"/>
       <c r="O23" s="5"/>
       <c r="P23" s="5"/>
       <c r="Q23" s="5"/>
-      <c r="R23" s="5"/>
-      <c r="S23" s="5"/>
-      <c r="T23" s="5"/>
-    </row>
-    <row r="24" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -1656,10 +1463,10 @@
         <v>6</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I24" s="5">
         <v>140</v>
@@ -1667,22 +1474,15 @@
       <c r="J24" s="5">
         <v>-100</v>
       </c>
-      <c r="K24" s="5">
-        <v>2</v>
-      </c>
+      <c r="K24" s="5"/>
       <c r="L24" s="5"/>
-      <c r="M24" s="5">
-        <v>0</v>
-      </c>
+      <c r="M24" s="5"/>
       <c r="N24" s="5"/>
       <c r="O24" s="5"/>
       <c r="P24" s="5"/>
       <c r="Q24" s="5"/>
-      <c r="R24" s="5"/>
-      <c r="S24" s="5"/>
-      <c r="T24" s="5"/>
-    </row>
-    <row r="25" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -1699,10 +1499,10 @@
         <v>3</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I25" s="5">
         <v>135</v>
@@ -1710,22 +1510,15 @@
       <c r="J25" s="5">
         <v>100</v>
       </c>
-      <c r="K25" s="5">
-        <v>2</v>
-      </c>
+      <c r="K25" s="5"/>
       <c r="L25" s="5"/>
-      <c r="M25" s="5">
-        <v>0</v>
-      </c>
+      <c r="M25" s="5"/>
       <c r="N25" s="5"/>
       <c r="O25" s="5"/>
       <c r="P25" s="5"/>
       <c r="Q25" s="5"/>
-      <c r="R25" s="5"/>
-      <c r="S25" s="5"/>
-      <c r="T25" s="5"/>
-    </row>
-    <row r="26" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -1741,29 +1534,22 @@
         <v>3</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
       <c r="J26" s="5">
         <v>-100</v>
       </c>
-      <c r="K26" s="5">
-        <v>1</v>
-      </c>
+      <c r="K26" s="5"/>
       <c r="L26" s="5"/>
-      <c r="M26" s="5">
-        <v>0</v>
-      </c>
+      <c r="M26" s="5"/>
       <c r="N26" s="5"/>
       <c r="O26" s="5"/>
       <c r="P26" s="5"/>
       <c r="Q26" s="5"/>
-      <c r="R26" s="5"/>
-      <c r="S26" s="5"/>
-      <c r="T26" s="5"/>
-    </row>
-    <row r="27" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -1779,29 +1565,22 @@
         <v>6</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
       <c r="J27" s="5">
         <v>100</v>
       </c>
-      <c r="K27" s="5">
-        <v>2</v>
-      </c>
+      <c r="K27" s="5"/>
       <c r="L27" s="5"/>
-      <c r="M27" s="5">
-        <v>0</v>
-      </c>
+      <c r="M27" s="5"/>
       <c r="N27" s="5"/>
       <c r="O27" s="5"/>
       <c r="P27" s="5"/>
       <c r="Q27" s="5"/>
-      <c r="R27" s="5"/>
-      <c r="S27" s="5"/>
-      <c r="T27" s="5"/>
-    </row>
-    <row r="28" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -1818,10 +1597,10 @@
         <v>3</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I28" s="5">
         <v>143</v>
@@ -1829,22 +1608,15 @@
       <c r="J28" s="5">
         <v>-100</v>
       </c>
-      <c r="K28" s="5">
-        <v>2</v>
-      </c>
+      <c r="K28" s="5"/>
       <c r="L28" s="5"/>
-      <c r="M28" s="5">
-        <v>0</v>
-      </c>
+      <c r="M28" s="5"/>
       <c r="N28" s="5"/>
       <c r="O28" s="5"/>
       <c r="P28" s="5"/>
       <c r="Q28" s="5"/>
-      <c r="R28" s="5"/>
-      <c r="S28" s="5"/>
-      <c r="T28" s="5"/>
-    </row>
-    <row r="29" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -1860,10 +1632,10 @@
         <v>9</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I29" s="5">
         <v>179</v>
@@ -1871,22 +1643,15 @@
       <c r="J29" s="5">
         <v>100</v>
       </c>
-      <c r="K29" s="5">
-        <v>2</v>
-      </c>
+      <c r="K29" s="5"/>
       <c r="L29" s="5"/>
-      <c r="M29" s="5">
-        <v>0</v>
-      </c>
+      <c r="M29" s="5"/>
       <c r="N29" s="5"/>
       <c r="O29" s="5"/>
       <c r="P29" s="5"/>
       <c r="Q29" s="5"/>
-      <c r="R29" s="5"/>
-      <c r="S29" s="5"/>
-      <c r="T29" s="5"/>
-    </row>
-    <row r="30" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -1902,29 +1667,22 @@
         <v>9</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
       <c r="J30" s="5">
         <v>-100</v>
       </c>
-      <c r="K30" s="5">
-        <v>1</v>
-      </c>
+      <c r="K30" s="5"/>
       <c r="L30" s="5"/>
-      <c r="M30" s="5">
-        <v>0</v>
-      </c>
+      <c r="M30" s="5"/>
       <c r="N30" s="5"/>
       <c r="O30" s="5"/>
       <c r="P30" s="5"/>
       <c r="Q30" s="5"/>
-      <c r="R30" s="5"/>
-      <c r="S30" s="5"/>
-      <c r="T30" s="5"/>
-    </row>
-    <row r="31" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -1940,10 +1698,10 @@
         <v>9</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I31" s="5">
         <v>192</v>
@@ -1951,22 +1709,15 @@
       <c r="J31" s="5">
         <v>100</v>
       </c>
-      <c r="K31" s="5">
-        <v>2</v>
-      </c>
+      <c r="K31" s="5"/>
       <c r="L31" s="5"/>
-      <c r="M31" s="5">
-        <v>0</v>
-      </c>
+      <c r="M31" s="5"/>
       <c r="N31" s="5"/>
       <c r="O31" s="5"/>
       <c r="P31" s="5"/>
       <c r="Q31" s="5"/>
-      <c r="R31" s="5"/>
-      <c r="S31" s="5"/>
-      <c r="T31" s="5"/>
-    </row>
-    <row r="32" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -1983,10 +1734,10 @@
         <v>3</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I32" s="5">
         <v>146</v>
@@ -1994,22 +1745,15 @@
       <c r="J32" s="5">
         <v>-100</v>
       </c>
-      <c r="K32" s="5">
-        <v>2</v>
-      </c>
+      <c r="K32" s="5"/>
       <c r="L32" s="5"/>
-      <c r="M32" s="5">
-        <v>0</v>
-      </c>
+      <c r="M32" s="5"/>
       <c r="N32" s="5"/>
       <c r="O32" s="5"/>
       <c r="P32" s="5"/>
       <c r="Q32" s="5"/>
-      <c r="R32" s="5"/>
-      <c r="S32" s="5"/>
-      <c r="T32" s="5"/>
-    </row>
-    <row r="33" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -2025,29 +1769,22 @@
         <v>3</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
       <c r="J33" s="5">
         <v>-100</v>
       </c>
-      <c r="K33" s="5">
-        <v>2</v>
-      </c>
+      <c r="K33" s="5"/>
       <c r="L33" s="5"/>
-      <c r="M33" s="5">
-        <v>0</v>
-      </c>
+      <c r="M33" s="5"/>
       <c r="N33" s="5"/>
       <c r="O33" s="5"/>
       <c r="P33" s="5"/>
       <c r="Q33" s="5"/>
-      <c r="R33" s="5"/>
-      <c r="S33" s="5"/>
-      <c r="T33" s="5"/>
-    </row>
-    <row r="34" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -2063,29 +1800,22 @@
         <v>6</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
       <c r="J34" s="5">
         <v>100</v>
       </c>
-      <c r="K34" s="5">
-        <v>2</v>
-      </c>
+      <c r="K34" s="5"/>
       <c r="L34" s="5"/>
-      <c r="M34" s="5">
-        <v>0</v>
-      </c>
+      <c r="M34" s="5"/>
       <c r="N34" s="5"/>
       <c r="O34" s="5"/>
       <c r="P34" s="5"/>
       <c r="Q34" s="5"/>
-      <c r="R34" s="5"/>
-      <c r="S34" s="5"/>
-      <c r="T34" s="5"/>
-    </row>
-    <row r="35" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -2101,29 +1831,22 @@
         <v>3</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
       <c r="J35" s="5">
         <v>100</v>
       </c>
-      <c r="K35" s="5">
-        <v>1</v>
-      </c>
+      <c r="K35" s="5"/>
       <c r="L35" s="5"/>
-      <c r="M35" s="5">
-        <v>0</v>
-      </c>
+      <c r="M35" s="5"/>
       <c r="N35" s="5"/>
       <c r="O35" s="5"/>
       <c r="P35" s="5"/>
       <c r="Q35" s="5"/>
-      <c r="R35" s="5"/>
-      <c r="S35" s="5"/>
-      <c r="T35" s="5"/>
-    </row>
-    <row r="36" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -2139,10 +1862,10 @@
         <v>9</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I36" s="5">
         <v>113</v>
@@ -2150,22 +1873,15 @@
       <c r="J36" s="5">
         <v>-100</v>
       </c>
-      <c r="K36" s="5">
-        <v>2</v>
-      </c>
+      <c r="K36" s="5"/>
       <c r="L36" s="5"/>
-      <c r="M36" s="5">
-        <v>0</v>
-      </c>
+      <c r="M36" s="5"/>
       <c r="N36" s="5"/>
       <c r="O36" s="5"/>
       <c r="P36" s="5"/>
       <c r="Q36" s="5"/>
-      <c r="R36" s="5"/>
-      <c r="S36" s="5"/>
-      <c r="T36" s="5"/>
-    </row>
-    <row r="37" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -2182,10 +1898,10 @@
         <v>3</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I37" s="5">
         <v>245</v>
@@ -2193,22 +1909,15 @@
       <c r="J37" s="5">
         <v>100</v>
       </c>
-      <c r="K37" s="5">
-        <v>2</v>
-      </c>
+      <c r="K37" s="5"/>
       <c r="L37" s="5"/>
-      <c r="M37" s="5">
-        <v>0</v>
-      </c>
+      <c r="M37" s="5"/>
       <c r="N37" s="5"/>
       <c r="O37" s="5"/>
       <c r="P37" s="5"/>
       <c r="Q37" s="5"/>
-      <c r="R37" s="5"/>
-      <c r="S37" s="5"/>
-      <c r="T37" s="5"/>
-    </row>
-    <row r="38" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -2224,29 +1933,22 @@
         <v>9</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
       <c r="J38" s="5">
         <v>100</v>
       </c>
-      <c r="K38" s="5">
-        <v>1</v>
-      </c>
+      <c r="K38" s="5"/>
       <c r="L38" s="5"/>
-      <c r="M38" s="5">
-        <v>0</v>
-      </c>
+      <c r="M38" s="5"/>
       <c r="N38" s="5"/>
       <c r="O38" s="5"/>
       <c r="P38" s="5"/>
       <c r="Q38" s="5"/>
-      <c r="R38" s="5"/>
-      <c r="S38" s="5"/>
-      <c r="T38" s="5"/>
-    </row>
-    <row r="39" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -2263,10 +1965,10 @@
         <v>6</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I39" s="5">
         <v>186</v>
@@ -2274,22 +1976,15 @@
       <c r="J39" s="5">
         <v>100</v>
       </c>
-      <c r="K39" s="5">
-        <v>2</v>
-      </c>
+      <c r="K39" s="5"/>
       <c r="L39" s="5"/>
-      <c r="M39" s="5">
-        <v>0</v>
-      </c>
+      <c r="M39" s="5"/>
       <c r="N39" s="5"/>
       <c r="O39" s="5"/>
       <c r="P39" s="5"/>
       <c r="Q39" s="5"/>
-      <c r="R39" s="5"/>
-      <c r="S39" s="5"/>
-      <c r="T39" s="5"/>
-    </row>
-    <row r="40" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -2305,29 +2000,22 @@
         <v>9</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
       <c r="J40" s="5">
         <v>-100</v>
       </c>
-      <c r="K40" s="5">
-        <v>2</v>
-      </c>
+      <c r="K40" s="5"/>
       <c r="L40" s="5"/>
-      <c r="M40" s="5">
-        <v>0</v>
-      </c>
+      <c r="M40" s="5"/>
       <c r="N40" s="5"/>
       <c r="O40" s="5"/>
       <c r="P40" s="5"/>
       <c r="Q40" s="5"/>
-      <c r="R40" s="5"/>
-      <c r="S40" s="5"/>
-      <c r="T40" s="5"/>
-    </row>
-    <row r="41" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -2343,29 +2031,22 @@
         <v>6</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
       <c r="J41" s="5">
         <v>100</v>
       </c>
-      <c r="K41" s="5">
-        <v>2</v>
-      </c>
+      <c r="K41" s="5"/>
       <c r="L41" s="5"/>
-      <c r="M41" s="5">
-        <v>0</v>
-      </c>
+      <c r="M41" s="5"/>
       <c r="N41" s="5"/>
       <c r="O41" s="5"/>
       <c r="P41" s="5"/>
       <c r="Q41" s="5"/>
-      <c r="R41" s="5"/>
-      <c r="S41" s="5"/>
-      <c r="T41" s="5"/>
-    </row>
-    <row r="42" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -2381,29 +2062,22 @@
         <v>3</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
       <c r="J42" s="5">
         <v>100</v>
       </c>
-      <c r="K42" s="5">
-        <v>2</v>
-      </c>
+      <c r="K42" s="5"/>
       <c r="L42" s="5"/>
-      <c r="M42" s="5">
-        <v>0</v>
-      </c>
+      <c r="M42" s="5"/>
       <c r="N42" s="5"/>
       <c r="O42" s="5"/>
       <c r="P42" s="5"/>
       <c r="Q42" s="5"/>
-      <c r="R42" s="5"/>
-      <c r="S42" s="5"/>
-      <c r="T42" s="5"/>
-    </row>
-    <row r="43" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -2419,10 +2093,10 @@
         <v>9</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I43" s="5">
         <v>99</v>
@@ -2430,22 +2104,15 @@
       <c r="J43" s="5">
         <v>100</v>
       </c>
-      <c r="K43" s="5">
-        <v>1</v>
-      </c>
+      <c r="K43" s="5"/>
       <c r="L43" s="5"/>
-      <c r="M43" s="5">
-        <v>0</v>
-      </c>
+      <c r="M43" s="5"/>
       <c r="N43" s="5"/>
       <c r="O43" s="5"/>
       <c r="P43" s="5"/>
       <c r="Q43" s="5"/>
-      <c r="R43" s="5"/>
-      <c r="S43" s="5"/>
-      <c r="T43" s="5"/>
-    </row>
-    <row r="44" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="11">
         <v>43</v>
       </c>
@@ -2461,29 +2128,22 @@
         <v>3</v>
       </c>
       <c r="G44" s="12" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H44" s="12"/>
       <c r="I44" s="12"/>
       <c r="J44" s="12">
         <v>-100</v>
       </c>
-      <c r="K44" s="12">
-        <v>2</v>
-      </c>
+      <c r="K44" s="12"/>
       <c r="L44" s="12"/>
-      <c r="M44" s="12">
-        <v>0</v>
-      </c>
+      <c r="M44" s="12"/>
       <c r="N44" s="12"/>
       <c r="O44" s="12"/>
       <c r="P44" s="12"/>
       <c r="Q44" s="12"/>
-      <c r="R44" s="12"/>
-      <c r="S44" s="12"/>
-      <c r="T44" s="12"/>
-    </row>
-    <row r="45" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -2499,29 +2159,22 @@
         <v>9</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
       <c r="J45" s="5">
         <v>-100</v>
       </c>
-      <c r="K45" s="5">
-        <v>2</v>
-      </c>
+      <c r="K45" s="5"/>
       <c r="L45" s="5"/>
-      <c r="M45" s="5">
-        <v>0</v>
-      </c>
+      <c r="M45" s="5"/>
       <c r="N45" s="5"/>
       <c r="O45" s="5"/>
       <c r="P45" s="5"/>
       <c r="Q45" s="5"/>
-      <c r="R45" s="5"/>
-      <c r="S45" s="5"/>
-      <c r="T45" s="5"/>
-    </row>
-    <row r="46" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -2538,10 +2191,10 @@
         <v>6</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I46" s="5">
         <v>76</v>
@@ -2549,22 +2202,15 @@
       <c r="J46" s="5">
         <v>100</v>
       </c>
-      <c r="K46" s="5">
-        <v>2</v>
-      </c>
+      <c r="K46" s="5"/>
       <c r="L46" s="5"/>
-      <c r="M46" s="5">
-        <v>0</v>
-      </c>
+      <c r="M46" s="5"/>
       <c r="N46" s="5"/>
       <c r="O46" s="5"/>
       <c r="P46" s="5"/>
       <c r="Q46" s="5"/>
-      <c r="R46" s="5"/>
-      <c r="S46" s="5"/>
-      <c r="T46" s="5"/>
-    </row>
-    <row r="47" spans="1:20" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:17" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -2577,19 +2223,13 @@
         <v>6</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J47" s="5">
         <v>-100</v>
       </c>
-      <c r="K47" s="5">
-        <v>1</v>
-      </c>
-      <c r="M47" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>47</v>
       </c>
@@ -2606,10 +2246,10 @@
         <v>6</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I48" s="5">
         <v>155</v>
@@ -2617,22 +2257,15 @@
       <c r="J48" s="5">
         <v>-100</v>
       </c>
-      <c r="K48" s="5">
-        <v>1</v>
-      </c>
+      <c r="K48" s="5"/>
       <c r="L48" s="5"/>
-      <c r="M48" s="5">
-        <v>0</v>
-      </c>
+      <c r="M48" s="5"/>
       <c r="N48" s="5"/>
       <c r="O48" s="5"/>
       <c r="P48" s="5"/>
       <c r="Q48" s="5"/>
-      <c r="R48" s="5"/>
-      <c r="S48" s="5"/>
-      <c r="T48" s="5"/>
-    </row>
-    <row r="49" spans="1:20" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:17" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="11">
         <v>48</v>
       </c>
@@ -2649,21 +2282,14 @@
         <v>6</v>
       </c>
       <c r="G49" s="12" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J49" s="12">
         <v>-100</v>
       </c>
-      <c r="K49" s="12">
-        <v>1</v>
-      </c>
-      <c r="L49" s="12"/>
-      <c r="M49" s="12">
-        <v>0</v>
-      </c>
-      <c r="N49" s="12"/>
-    </row>
-    <row r="50" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K49" s="12"/>
+    </row>
+    <row r="50" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -2680,25 +2306,18 @@
         <v>3</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I50" s="3"/>
       <c r="J50" s="5">
         <v>100</v>
       </c>
-      <c r="K50" s="5">
-        <v>1</v>
-      </c>
-      <c r="L50" s="5"/>
-      <c r="M50" s="5">
-        <v>0</v>
-      </c>
-      <c r="N50" s="5"/>
-    </row>
-    <row r="51" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K50" s="5"/>
+    </row>
+    <row r="51" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>50</v>
       </c>
@@ -2714,10 +2333,10 @@
         <v>3</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I51" s="5">
         <v>209</v>
@@ -2725,17 +2344,10 @@
       <c r="J51" s="5">
         <v>100</v>
       </c>
-      <c r="K51" s="5">
-        <v>1</v>
-      </c>
+      <c r="K51" s="5"/>
       <c r="L51" s="5"/>
-      <c r="M51" s="5">
-        <v>0</v>
-      </c>
-      <c r="N51" s="5"/>
-      <c r="O51" s="5"/>
-    </row>
-    <row r="52" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>51</v>
       </c>
@@ -2752,10 +2364,10 @@
         <v>3</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I52" s="5">
         <v>243</v>
@@ -2763,16 +2375,9 @@
       <c r="J52" s="5">
         <v>-100</v>
       </c>
-      <c r="K52" s="5">
-        <v>1</v>
-      </c>
-      <c r="L52" s="5"/>
-      <c r="M52" s="5">
-        <v>0</v>
-      </c>
-      <c r="N52" s="5"/>
-    </row>
-    <row r="53" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K52" s="5"/>
+    </row>
+    <row r="53" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>52</v>
       </c>
@@ -2789,10 +2394,10 @@
         <v>6</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="I53" s="5">
         <v>150</v>
@@ -2801,25 +2406,18 @@
         <v>-100</v>
       </c>
       <c r="K53" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L53" s="5">
-        <v>2</v>
-      </c>
-      <c r="M53" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M53" s="5"/>
       <c r="N53" s="5"/>
-      <c r="O53" s="5">
-        <v>0</v>
-      </c>
+      <c r="O53" s="5"/>
       <c r="P53" s="5"/>
       <c r="Q53" s="5"/>
-      <c r="R53" s="5"/>
-      <c r="S53" s="5"/>
-      <c r="T53" s="5"/>
-    </row>
-    <row r="54" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>53</v>
       </c>
@@ -2836,7 +2434,7 @@
         <v>6</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
@@ -2844,25 +2442,18 @@
         <v>100</v>
       </c>
       <c r="K54" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L54" s="5">
-        <v>2</v>
-      </c>
-      <c r="M54" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M54" s="5"/>
       <c r="N54" s="5"/>
-      <c r="O54" s="5">
-        <v>0</v>
-      </c>
+      <c r="O54" s="5"/>
       <c r="P54" s="5"/>
       <c r="Q54" s="5"/>
-      <c r="R54" s="5"/>
-      <c r="S54" s="5"/>
-      <c r="T54" s="5"/>
-    </row>
-    <row r="55" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>54</v>
       </c>
@@ -2875,10 +2466,10 @@
         <v>3</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="I55" s="5">
         <v>493</v>
@@ -2890,17 +2481,10 @@
         <v>2</v>
       </c>
       <c r="L55" s="5">
-        <v>2</v>
-      </c>
-      <c r="M55" s="5">
-        <v>0</v>
-      </c>
-      <c r="N55" s="5"/>
-      <c r="O55" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>55</v>
       </c>
@@ -2917,10 +2501,10 @@
         <v>3</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I56" s="5">
         <v>182</v>
@@ -2929,20 +2513,13 @@
         <v>-100</v>
       </c>
       <c r="K56" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L56" s="5">
-        <v>2</v>
-      </c>
-      <c r="M56" s="5">
-        <v>0</v>
-      </c>
-      <c r="N56" s="5"/>
-      <c r="O56" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>56</v>
       </c>
@@ -2959,10 +2536,10 @@
         <v>6</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="I57" s="5">
         <v>195</v>
@@ -2971,20 +2548,13 @@
         <v>100</v>
       </c>
       <c r="K57" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L57" s="5">
-        <v>2</v>
-      </c>
-      <c r="M57" s="5">
-        <v>0</v>
-      </c>
-      <c r="N57" s="5"/>
-      <c r="O57" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <v>57</v>
       </c>
@@ -2998,7 +2568,7 @@
         <v>3</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
@@ -3006,25 +2576,18 @@
         <v>100</v>
       </c>
       <c r="K58" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L58" s="5">
-        <v>2</v>
-      </c>
-      <c r="M58" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M58" s="5"/>
       <c r="N58" s="5"/>
-      <c r="O58" s="5">
-        <v>0</v>
-      </c>
+      <c r="O58" s="5"/>
       <c r="P58" s="5"/>
       <c r="Q58" s="5"/>
-      <c r="R58" s="5"/>
-      <c r="S58" s="5"/>
-      <c r="T58" s="5"/>
-    </row>
-    <row r="59" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>58</v>
       </c>
@@ -3041,10 +2604,10 @@
         <v>6</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I59" s="5">
         <v>141</v>
@@ -3053,20 +2616,13 @@
         <v>100</v>
       </c>
       <c r="K59" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L59" s="5">
-        <v>2</v>
-      </c>
-      <c r="M59" s="5">
-        <v>0</v>
-      </c>
-      <c r="N59" s="5"/>
-      <c r="O59" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>59</v>
       </c>
@@ -3083,10 +2639,10 @@
         <v>3</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I60" s="5">
         <v>115</v>
@@ -3095,20 +2651,13 @@
         <v>100</v>
       </c>
       <c r="K60" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L60" s="5">
-        <v>2</v>
-      </c>
-      <c r="M60" s="5">
-        <v>0</v>
-      </c>
-      <c r="N60" s="5"/>
-      <c r="O60" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <v>60</v>
       </c>
@@ -3124,10 +2673,10 @@
         <v>3</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I61" s="5">
         <v>315</v>
@@ -3136,20 +2685,13 @@
         <v>-100</v>
       </c>
       <c r="K61" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L61" s="5">
-        <v>2</v>
-      </c>
-      <c r="M61" s="5">
-        <v>0</v>
-      </c>
-      <c r="N61" s="5"/>
-      <c r="O61" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <v>61</v>
       </c>
@@ -3166,10 +2708,10 @@
         <v>3</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I62" s="5">
         <v>114</v>
@@ -3178,20 +2720,13 @@
         <v>-100</v>
       </c>
       <c r="K62" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L62" s="5">
-        <v>2</v>
-      </c>
-      <c r="M62" s="5">
-        <v>0</v>
-      </c>
-      <c r="N62" s="5"/>
-      <c r="O62" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <v>62</v>
       </c>
@@ -3208,7 +2743,7 @@
         <v>3</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H63" s="5"/>
       <c r="I63" s="5"/>
@@ -3216,25 +2751,18 @@
         <v>-100</v>
       </c>
       <c r="K63" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L63" s="5">
-        <v>2</v>
-      </c>
-      <c r="M63" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M63" s="5"/>
       <c r="N63" s="5"/>
-      <c r="O63" s="5">
-        <v>0</v>
-      </c>
+      <c r="O63" s="5"/>
       <c r="P63" s="5"/>
       <c r="Q63" s="5"/>
-      <c r="R63" s="5"/>
-      <c r="S63" s="5"/>
-      <c r="T63" s="5"/>
-    </row>
-    <row r="64" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <v>63</v>
       </c>
@@ -3251,10 +2779,10 @@
         <v>6</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I64" s="5">
         <v>248</v>
@@ -3263,20 +2791,13 @@
         <v>-100</v>
       </c>
       <c r="K64" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L64" s="5">
-        <v>2</v>
-      </c>
-      <c r="M64" s="5">
-        <v>0</v>
-      </c>
-      <c r="N64" s="5"/>
-      <c r="O64" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <v>64</v>
       </c>
@@ -3293,10 +2814,10 @@
         <v>6</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I65" s="5">
         <v>158</v>
@@ -3305,20 +2826,13 @@
         <v>100</v>
       </c>
       <c r="K65" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L65" s="5">
-        <v>2</v>
-      </c>
-      <c r="M65" s="5">
-        <v>0</v>
-      </c>
-      <c r="N65" s="5"/>
-      <c r="O65" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <v>65</v>
       </c>
@@ -3335,7 +2849,7 @@
         <v>6</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H66" s="5"/>
       <c r="I66" s="5"/>
@@ -3343,25 +2857,18 @@
         <v>-100</v>
       </c>
       <c r="K66" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L66" s="5">
-        <v>2</v>
-      </c>
-      <c r="M66" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M66" s="5"/>
       <c r="N66" s="5"/>
-      <c r="O66" s="5">
-        <v>0</v>
-      </c>
+      <c r="O66" s="5"/>
       <c r="P66" s="5"/>
       <c r="Q66" s="5"/>
-      <c r="R66" s="5"/>
-      <c r="S66" s="5"/>
-      <c r="T66" s="5"/>
-    </row>
-    <row r="67" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <v>66</v>
       </c>
@@ -3378,10 +2885,10 @@
         <v>3</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I67" s="5">
         <v>135</v>
@@ -3390,25 +2897,18 @@
         <v>100</v>
       </c>
       <c r="K67" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L67" s="5">
-        <v>2</v>
-      </c>
-      <c r="M67" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M67" s="5"/>
       <c r="N67" s="5"/>
-      <c r="O67" s="5">
-        <v>0</v>
-      </c>
+      <c r="O67" s="5"/>
       <c r="P67" s="5"/>
       <c r="Q67" s="5"/>
-      <c r="R67" s="5"/>
-      <c r="S67" s="5"/>
-      <c r="T67" s="5"/>
-    </row>
-    <row r="68" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="68" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>67</v>
       </c>
@@ -3422,7 +2922,7 @@
         <v>3</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H68" s="5"/>
       <c r="I68" s="5"/>
@@ -3433,22 +2933,15 @@
         <v>1</v>
       </c>
       <c r="L68" s="5">
-        <v>1</v>
-      </c>
-      <c r="M68" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M68" s="5"/>
       <c r="N68" s="5"/>
-      <c r="O68" s="5">
-        <v>0</v>
-      </c>
+      <c r="O68" s="5"/>
       <c r="P68" s="5"/>
       <c r="Q68" s="5"/>
-      <c r="R68" s="5"/>
-      <c r="S68" s="5"/>
-      <c r="T68" s="5"/>
-    </row>
-    <row r="69" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="69" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
         <v>68</v>
       </c>
@@ -3465,10 +2958,10 @@
         <v>6</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I69" s="5">
         <v>110</v>
@@ -3480,22 +2973,15 @@
         <v>1</v>
       </c>
       <c r="L69" s="5">
-        <v>1</v>
-      </c>
-      <c r="M69" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M69" s="5"/>
       <c r="N69" s="5"/>
-      <c r="O69" s="5">
-        <v>0</v>
-      </c>
+      <c r="O69" s="5"/>
       <c r="P69" s="5"/>
       <c r="Q69" s="5"/>
-      <c r="R69" s="5"/>
-      <c r="S69" s="5"/>
-      <c r="T69" s="5"/>
-    </row>
-    <row r="70" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
         <v>69</v>
       </c>
@@ -3512,10 +2998,10 @@
         <v>6</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I70" s="5">
         <v>270</v>
@@ -3524,25 +3010,18 @@
         <v>-100</v>
       </c>
       <c r="K70" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L70" s="5">
-        <v>1</v>
-      </c>
-      <c r="M70" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M70" s="5"/>
       <c r="N70" s="5"/>
-      <c r="O70" s="5">
-        <v>0</v>
-      </c>
+      <c r="O70" s="5"/>
       <c r="P70" s="5"/>
       <c r="Q70" s="5"/>
-      <c r="R70" s="5"/>
-      <c r="S70" s="5"/>
-      <c r="T70" s="5"/>
-    </row>
-    <row r="71" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
         <v>70</v>
       </c>
@@ -3559,10 +3038,10 @@
         <v>6</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I71" s="5">
         <v>404</v>
@@ -3574,22 +3053,15 @@
         <v>1</v>
       </c>
       <c r="L71" s="5">
-        <v>1</v>
-      </c>
-      <c r="M71" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M71" s="5"/>
       <c r="N71" s="5"/>
-      <c r="O71" s="5">
-        <v>0</v>
-      </c>
+      <c r="O71" s="5"/>
       <c r="P71" s="5"/>
       <c r="Q71" s="5"/>
-      <c r="R71" s="5"/>
-      <c r="S71" s="5"/>
-      <c r="T71" s="5"/>
-    </row>
-    <row r="72" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
         <v>71</v>
       </c>
@@ -3606,10 +3078,10 @@
         <v>3</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I72" s="5">
         <v>70</v>
@@ -3618,25 +3090,18 @@
         <v>100</v>
       </c>
       <c r="K72" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L72" s="5">
-        <v>1</v>
-      </c>
-      <c r="M72" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M72" s="5"/>
       <c r="N72" s="5"/>
-      <c r="O72" s="5">
-        <v>0</v>
-      </c>
+      <c r="O72" s="5"/>
       <c r="P72" s="5"/>
       <c r="Q72" s="5"/>
-      <c r="R72" s="5"/>
-      <c r="S72" s="5"/>
-      <c r="T72" s="5"/>
-    </row>
-    <row r="73" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="73" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
         <v>72</v>
       </c>
@@ -3653,10 +3118,10 @@
         <v>6</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="I73" s="5">
         <v>239</v>
@@ -3668,22 +3133,15 @@
         <v>2</v>
       </c>
       <c r="L73" s="5">
-        <v>2</v>
-      </c>
-      <c r="M73" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M73" s="5"/>
       <c r="N73" s="5"/>
-      <c r="O73" s="5">
-        <v>0</v>
-      </c>
+      <c r="O73" s="5"/>
       <c r="P73" s="5"/>
       <c r="Q73" s="5"/>
-      <c r="R73" s="5"/>
-      <c r="S73" s="5"/>
-      <c r="T73" s="5"/>
-    </row>
-    <row r="74" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
         <v>73</v>
       </c>
@@ -3700,10 +3158,10 @@
         <v>6</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I74" s="5">
         <v>60</v>
@@ -3715,17 +3173,10 @@
         <v>1</v>
       </c>
       <c r="L74" s="5">
-        <v>1</v>
-      </c>
-      <c r="M74" s="5">
-        <v>0</v>
-      </c>
-      <c r="N74" s="5"/>
-      <c r="O74" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
         <v>74</v>
       </c>
@@ -3742,10 +3193,10 @@
         <v>6</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I75" s="5">
         <v>113</v>
@@ -3754,25 +3205,18 @@
         <v>100</v>
       </c>
       <c r="K75" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L75" s="5">
-        <v>1</v>
-      </c>
-      <c r="M75" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M75" s="5"/>
       <c r="N75" s="5"/>
-      <c r="O75" s="5">
-        <v>0</v>
-      </c>
+      <c r="O75" s="5"/>
       <c r="P75" s="5"/>
       <c r="Q75" s="5"/>
-      <c r="R75" s="5"/>
-      <c r="S75" s="5"/>
-      <c r="T75" s="5"/>
-    </row>
-    <row r="76" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
         <v>75</v>
       </c>
@@ -3789,10 +3233,10 @@
         <v>6</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I76" s="5">
         <v>88</v>
@@ -3801,20 +3245,13 @@
         <v>-100</v>
       </c>
       <c r="K76" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L76" s="5">
-        <v>1</v>
-      </c>
-      <c r="M76" s="5">
-        <v>0</v>
-      </c>
-      <c r="N76" s="5"/>
-      <c r="O76" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
         <v>76</v>
       </c>
@@ -3828,26 +3265,19 @@
         <v>6</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J77" s="5">
         <v>-100</v>
       </c>
       <c r="K77" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L77" s="5">
-        <v>1</v>
-      </c>
-      <c r="M77" s="5">
-        <v>0</v>
-      </c>
-      <c r="N77" s="5"/>
-      <c r="O77" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
         <v>77</v>
       </c>
@@ -3864,10 +3294,10 @@
         <v>6</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I78" s="5">
         <v>88</v>
@@ -3876,25 +3306,18 @@
         <v>-100</v>
       </c>
       <c r="K78" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L78" s="5">
-        <v>1</v>
-      </c>
-      <c r="M78" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M78" s="5"/>
       <c r="N78" s="5"/>
-      <c r="O78" s="5">
-        <v>0</v>
-      </c>
+      <c r="O78" s="5"/>
       <c r="P78" s="5"/>
       <c r="Q78" s="5"/>
-      <c r="R78" s="5"/>
-      <c r="S78" s="5"/>
-      <c r="T78" s="5"/>
-    </row>
-    <row r="79" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="79" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
         <v>78</v>
       </c>
@@ -3911,10 +3334,10 @@
         <v>6</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="I79" s="5">
         <v>105</v>
@@ -3926,22 +3349,15 @@
         <v>1</v>
       </c>
       <c r="L79" s="5">
-        <v>1</v>
-      </c>
-      <c r="M79" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M79" s="5"/>
       <c r="N79" s="5"/>
-      <c r="O79" s="5">
-        <v>0</v>
-      </c>
+      <c r="O79" s="5"/>
       <c r="P79" s="5"/>
       <c r="Q79" s="5"/>
-      <c r="R79" s="5"/>
-      <c r="S79" s="5"/>
-      <c r="T79" s="5"/>
-    </row>
-    <row r="80" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="80" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
         <v>79</v>
       </c>
@@ -3955,26 +3371,19 @@
         <v>3</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J80" s="5">
         <v>-100</v>
       </c>
       <c r="K80" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L80" s="5">
-        <v>1</v>
-      </c>
-      <c r="M80" s="5">
-        <v>0</v>
-      </c>
-      <c r="N80" s="5"/>
-      <c r="O80" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
         <v>80</v>
       </c>
@@ -3986,25 +3395,19 @@
         <v>3</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J81" s="5">
         <v>-100</v>
       </c>
       <c r="K81" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L81" s="5">
-        <v>1</v>
-      </c>
-      <c r="M81" s="4">
-        <v>0</v>
-      </c>
-      <c r="O81" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
         <v>81</v>
       </c>
@@ -4021,10 +3424,10 @@
         <v>6</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I82" s="5">
         <v>55</v>
@@ -4036,22 +3439,15 @@
         <v>1</v>
       </c>
       <c r="L82" s="5">
-        <v>1</v>
-      </c>
-      <c r="M82" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M82" s="5"/>
       <c r="N82" s="5"/>
-      <c r="O82" s="5">
-        <v>0</v>
-      </c>
+      <c r="O82" s="5"/>
       <c r="P82" s="5"/>
       <c r="Q82" s="5"/>
-      <c r="R82" s="5"/>
-      <c r="S82" s="5"/>
-      <c r="T82" s="5"/>
-    </row>
-    <row r="83" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="83" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
         <v>82</v>
       </c>
@@ -4065,7 +3461,7 @@
         <v>3</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J83" s="5">
         <v>-100</v>
@@ -4074,17 +3470,10 @@
         <v>1</v>
       </c>
       <c r="L83" s="5">
-        <v>1</v>
-      </c>
-      <c r="M83" s="5">
-        <v>0</v>
-      </c>
-      <c r="N83" s="5"/>
-      <c r="O83" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
         <v>83</v>
       </c>
@@ -4098,7 +3487,7 @@
         <v>3</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J84" s="5">
         <v>-100</v>
@@ -4107,17 +3496,10 @@
         <v>1</v>
       </c>
       <c r="L84" s="5">
-        <v>1</v>
-      </c>
-      <c r="M84" s="5">
-        <v>0</v>
-      </c>
-      <c r="N84" s="5"/>
-      <c r="O84" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
         <v>84</v>
       </c>
@@ -4131,7 +3513,7 @@
         <v>3</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H85" s="5"/>
       <c r="I85" s="5"/>
@@ -4142,22 +3524,15 @@
         <v>1</v>
       </c>
       <c r="L85" s="5">
-        <v>1</v>
-      </c>
-      <c r="M85" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M85" s="5"/>
       <c r="N85" s="5"/>
-      <c r="O85" s="5">
-        <v>0</v>
-      </c>
+      <c r="O85" s="5"/>
       <c r="P85" s="5"/>
       <c r="Q85" s="5"/>
-      <c r="R85" s="5"/>
-      <c r="S85" s="5"/>
-      <c r="T85" s="5"/>
-    </row>
-    <row r="86" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="86" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
         <v>85</v>
       </c>
@@ -4171,7 +3546,7 @@
         <v>3</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J86" s="5">
         <v>-100</v>
@@ -4179,15 +3554,8 @@
       <c r="K86" s="5">
         <v>1</v>
       </c>
-      <c r="L86" s="5">
-        <v>1</v>
-      </c>
-      <c r="M86" s="5">
-        <v>0</v>
-      </c>
-      <c r="N86" s="5"/>
-    </row>
-    <row r="87" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="87" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
         <v>86</v>
       </c>
@@ -4201,7 +3569,7 @@
         <v>3</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H87" s="5"/>
       <c r="I87" s="5"/>
@@ -4212,22 +3580,15 @@
         <v>1</v>
       </c>
       <c r="L87" s="5">
-        <v>1</v>
-      </c>
-      <c r="M87" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M87" s="5"/>
       <c r="N87" s="5"/>
-      <c r="O87" s="5">
-        <v>0</v>
-      </c>
+      <c r="O87" s="5"/>
       <c r="P87" s="5"/>
       <c r="Q87" s="5"/>
-      <c r="R87" s="5"/>
-      <c r="S87" s="5"/>
-      <c r="T87" s="5"/>
-    </row>
-    <row r="88" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="88" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
         <v>87</v>
       </c>
@@ -4241,7 +3602,7 @@
         <v>3</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H88" s="5"/>
       <c r="I88" s="5"/>
@@ -4251,21 +3612,14 @@
       <c r="K88" s="5">
         <v>1</v>
       </c>
-      <c r="L88" s="5">
-        <v>1</v>
-      </c>
-      <c r="M88" s="5">
-        <v>0</v>
-      </c>
+      <c r="L88" s="5"/>
+      <c r="M88" s="5"/>
       <c r="N88" s="5"/>
       <c r="O88" s="5"/>
       <c r="P88" s="5"/>
       <c r="Q88" s="5"/>
-      <c r="R88" s="5"/>
-      <c r="S88" s="5"/>
-      <c r="T88" s="5"/>
-    </row>
-    <row r="89" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="89" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
         <v>88</v>
       </c>
@@ -4281,10 +3635,10 @@
         <v>6</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H89" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I89" s="5">
         <v>103</v>
@@ -4293,27 +3647,18 @@
         <v>100</v>
       </c>
       <c r="K89" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L89" s="5">
-        <v>2</v>
-      </c>
-      <c r="M89" s="5">
-        <v>1</v>
-      </c>
-      <c r="N89" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="O89" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M89" s="5"/>
+      <c r="N89" s="5"/>
+      <c r="O89" s="5"/>
       <c r="P89" s="5"/>
       <c r="Q89" s="5"/>
-      <c r="R89" s="5"/>
-      <c r="S89" s="5"/>
-      <c r="T89" s="5"/>
-    </row>
-    <row r="90" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="90" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
         <v>89</v>
       </c>
@@ -4327,7 +3672,7 @@
         <v>3</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H90" s="5"/>
       <c r="I90" s="5"/>
@@ -4337,21 +3682,14 @@
       <c r="K90" s="5">
         <v>1</v>
       </c>
-      <c r="L90" s="5">
-        <v>1</v>
-      </c>
-      <c r="M90" s="5">
-        <v>0</v>
-      </c>
+      <c r="L90" s="5"/>
+      <c r="M90" s="5"/>
       <c r="N90" s="5"/>
       <c r="O90" s="5"/>
       <c r="P90" s="5"/>
       <c r="Q90" s="5"/>
-      <c r="R90" s="5"/>
-      <c r="S90" s="5"/>
-      <c r="T90" s="5"/>
-    </row>
-    <row r="91" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="91" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
         <v>90</v>
       </c>
@@ -4368,10 +3706,10 @@
         <v>6</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I91" s="5">
         <v>245</v>
@@ -4383,24 +3721,15 @@
         <v>2</v>
       </c>
       <c r="L91" s="5">
-        <v>2</v>
-      </c>
-      <c r="M91" s="5">
-        <v>1</v>
-      </c>
-      <c r="N91" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="O91" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M91" s="5"/>
+      <c r="N91" s="5"/>
+      <c r="O91" s="5"/>
       <c r="P91" s="5"/>
       <c r="Q91" s="5"/>
-      <c r="R91" s="5"/>
-      <c r="S91" s="5"/>
-      <c r="T91" s="5"/>
-    </row>
-    <row r="92" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="92" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
         <v>91</v>
       </c>
@@ -4416,10 +3745,10 @@
         <v>6</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="I92" s="5">
         <v>388</v>
@@ -4431,22 +3760,15 @@
         <v>2</v>
       </c>
       <c r="L92" s="5">
-        <v>2</v>
-      </c>
-      <c r="M92" s="5" t="s">
-        <v>64</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M92" s="5"/>
       <c r="N92" s="5"/>
-      <c r="O92" s="5">
-        <v>0</v>
-      </c>
+      <c r="O92" s="5"/>
       <c r="P92" s="5"/>
       <c r="Q92" s="5"/>
-      <c r="R92" s="5"/>
-      <c r="S92" s="5"/>
-      <c r="T92" s="5"/>
-    </row>
-    <row r="93" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="93" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
         <v>92</v>
       </c>
@@ -4463,10 +3785,10 @@
         <v>6</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I93" s="5">
         <v>114</v>
@@ -4478,24 +3800,15 @@
         <v>2</v>
       </c>
       <c r="L93" s="5">
-        <v>2</v>
-      </c>
-      <c r="M93" s="5">
-        <v>1</v>
-      </c>
-      <c r="N93" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="O93" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M93" s="5"/>
+      <c r="N93" s="5"/>
+      <c r="O93" s="5"/>
       <c r="P93" s="5"/>
       <c r="Q93" s="5"/>
-      <c r="R93" s="5"/>
-      <c r="S93" s="5"/>
-      <c r="T93" s="5"/>
-    </row>
-    <row r="94" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="94" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
         <v>93</v>
       </c>
@@ -4509,7 +3822,7 @@
         <v>3</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H94" s="5"/>
       <c r="I94" s="5">
@@ -4522,22 +3835,15 @@
         <v>1</v>
       </c>
       <c r="L94" s="5">
-        <v>1</v>
-      </c>
-      <c r="M94" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M94" s="5"/>
       <c r="N94" s="5"/>
-      <c r="O94" s="5">
-        <v>0</v>
-      </c>
+      <c r="O94" s="5"/>
       <c r="P94" s="5"/>
       <c r="Q94" s="5"/>
-      <c r="R94" s="5"/>
-      <c r="S94" s="5"/>
-      <c r="T94" s="5"/>
-    </row>
-    <row r="95" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="95" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
         <v>94</v>
       </c>
@@ -4554,10 +3860,10 @@
         <v>3</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="I95" s="5">
         <v>85</v>
@@ -4569,22 +3875,15 @@
         <v>1</v>
       </c>
       <c r="L95" s="5">
-        <v>1</v>
-      </c>
-      <c r="M95" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M95" s="5"/>
       <c r="N95" s="5"/>
-      <c r="O95" s="5">
-        <v>0</v>
-      </c>
+      <c r="O95" s="5"/>
       <c r="P95" s="5"/>
       <c r="Q95" s="5"/>
-      <c r="R95" s="5"/>
-      <c r="S95" s="5"/>
-      <c r="T95" s="5"/>
-    </row>
-    <row r="96" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="96" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
         <v>95</v>
       </c>
@@ -4598,7 +3897,7 @@
         <v>3</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H96" s="5"/>
       <c r="I96" s="5"/>
@@ -4608,19 +3907,14 @@
       <c r="K96" s="5">
         <v>1</v>
       </c>
-      <c r="L96" s="5">
-        <v>1</v>
-      </c>
+      <c r="L96" s="5"/>
       <c r="M96" s="5"/>
       <c r="N96" s="5"/>
       <c r="O96" s="5"/>
       <c r="P96" s="5"/>
       <c r="Q96" s="5"/>
-      <c r="R96" s="5"/>
-      <c r="S96" s="5"/>
-      <c r="T96" s="5"/>
-    </row>
-    <row r="97" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="97" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
         <v>96</v>
       </c>
@@ -4637,10 +3931,10 @@
         <v>3</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="I97" s="5">
         <v>220</v>
@@ -4652,22 +3946,15 @@
         <v>1</v>
       </c>
       <c r="L97" s="5">
-        <v>1</v>
-      </c>
-      <c r="M97" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M97" s="5"/>
       <c r="N97" s="5"/>
-      <c r="O97" s="5">
-        <v>0</v>
-      </c>
+      <c r="O97" s="5"/>
       <c r="P97" s="5"/>
       <c r="Q97" s="5"/>
-      <c r="R97" s="5"/>
-      <c r="S97" s="5"/>
-      <c r="T97" s="5"/>
-    </row>
-    <row r="98" spans="1:20" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="98" spans="1:17" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="19">
         <v>97</v>
       </c>
@@ -4680,7 +3967,7 @@
         <v>3</v>
       </c>
       <c r="G98" s="21" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J98" s="21">
         <v>100</v>
@@ -4689,16 +3976,10 @@
         <v>1</v>
       </c>
       <c r="L98" s="21">
-        <v>1</v>
-      </c>
-      <c r="M98" s="21">
-        <v>0</v>
-      </c>
-      <c r="O98" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:20" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" s="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="19">
         <v>98</v>
       </c>
@@ -4711,28 +3992,19 @@
         <v>6</v>
       </c>
       <c r="G99" s="21" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J99" s="21">
         <v>0</v>
       </c>
       <c r="K99" s="21">
-        <v>2</v>
-      </c>
-      <c r="L99" s="21">
-        <v>1</v>
-      </c>
-      <c r="M99" s="21">
-        <v>1</v>
-      </c>
-      <c r="N99" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="O99" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="L99" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
         <v>99</v>
       </c>
@@ -4749,10 +4021,10 @@
         <v>3</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I100" s="5">
         <f>60*2+15</f>
@@ -4765,22 +4037,15 @@
         <v>1</v>
       </c>
       <c r="L100" s="5">
-        <v>1</v>
-      </c>
-      <c r="M100" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M100" s="5"/>
       <c r="N100" s="5"/>
-      <c r="O100" s="5">
-        <v>0</v>
-      </c>
+      <c r="O100" s="5"/>
       <c r="P100" s="5"/>
       <c r="Q100" s="5"/>
-      <c r="R100" s="5"/>
-      <c r="S100" s="5"/>
-      <c r="T100" s="5"/>
-    </row>
-    <row r="101" spans="1:20" s="4" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="101" spans="1:17" s="4" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
         <v>100</v>
       </c>
@@ -4797,10 +4062,10 @@
         <v>3</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I101" s="5">
         <f>60+55</f>
@@ -4813,22 +4078,15 @@
         <v>1</v>
       </c>
       <c r="L101" s="5">
-        <v>1</v>
-      </c>
-      <c r="M101" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M101" s="5"/>
       <c r="N101" s="5"/>
-      <c r="O101" s="5">
-        <v>0</v>
-      </c>
+      <c r="O101" s="5"/>
       <c r="P101" s="5"/>
       <c r="Q101" s="5"/>
-      <c r="R101" s="5"/>
-      <c r="S101" s="5"/>
-      <c r="T101" s="5"/>
-    </row>
-    <row r="102" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="102" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
         <v>101</v>
       </c>
@@ -4844,10 +4102,10 @@
         <v>6</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="I102" s="4">
         <f>60+15</f>
@@ -4860,16 +4118,10 @@
         <v>1</v>
       </c>
       <c r="L102" s="5">
-        <v>1</v>
-      </c>
-      <c r="M102" s="5">
-        <v>1</v>
-      </c>
-      <c r="O102" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
         <v>102</v>
       </c>
@@ -4885,10 +4137,10 @@
         <v>3</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H103" s="5" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="I103" s="5">
         <f>36</f>
@@ -4901,16 +4153,10 @@
         <v>2</v>
       </c>
       <c r="L103" s="5">
-        <v>2</v>
-      </c>
-      <c r="M103" s="5">
-        <v>0</v>
-      </c>
-      <c r="O103" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
         <v>103</v>
       </c>
@@ -4926,10 +4172,10 @@
         <v>3</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H104" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="I104" s="5">
         <v>96</v>
@@ -4938,25 +4184,18 @@
         <v>100</v>
       </c>
       <c r="K104" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L104" s="5">
-        <v>2</v>
-      </c>
-      <c r="M104" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M104" s="5"/>
       <c r="N104" s="5"/>
-      <c r="O104" s="5">
-        <v>0</v>
-      </c>
+      <c r="O104" s="5"/>
       <c r="P104" s="5"/>
       <c r="Q104" s="5"/>
-      <c r="R104" s="5"/>
-      <c r="S104" s="5"/>
-      <c r="T104" s="5"/>
-    </row>
-    <row r="105" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="105" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
         <v>104</v>
       </c>
@@ -4972,10 +4211,10 @@
         <v>3</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I105" s="5">
         <f>60*2+23</f>
@@ -4988,22 +4227,15 @@
         <v>2</v>
       </c>
       <c r="L105" s="5">
-        <v>2</v>
-      </c>
-      <c r="M105" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M105" s="5"/>
       <c r="N105" s="5"/>
-      <c r="O105" s="5">
-        <v>0</v>
-      </c>
+      <c r="O105" s="5"/>
       <c r="P105" s="5"/>
       <c r="Q105" s="5"/>
-      <c r="R105" s="5"/>
-      <c r="S105" s="5"/>
-      <c r="T105" s="5"/>
-    </row>
-    <row r="106" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="106" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
         <v>105</v>
       </c>
@@ -5016,13 +4248,13 @@
         <v>3</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="O106" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="L106" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
         <v>106</v>
       </c>
@@ -5035,13 +4267,13 @@
         <v>3</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="O107" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="L107" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
         <v>107</v>
       </c>
@@ -5054,16 +4286,16 @@
         <v>6</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J108" s="5">
         <v>0</v>
       </c>
-      <c r="O108" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L108" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
         <v>108</v>
       </c>
@@ -5076,16 +4308,16 @@
         <v>6</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J109" s="5">
         <v>0</v>
       </c>
-      <c r="O109" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L109" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
         <v>109</v>
       </c>
@@ -5101,10 +4333,10 @@
         <v>6</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H110" s="9" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="I110" s="4">
         <f>67</f>
@@ -5114,19 +4346,13 @@
         <v>0</v>
       </c>
       <c r="K110" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L110" s="5">
-        <v>2</v>
-      </c>
-      <c r="M110" s="5">
-        <v>0</v>
-      </c>
-      <c r="O110" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
         <v>110</v>
       </c>
@@ -5143,10 +4369,10 @@
         <v>3</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H111" s="5" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="I111" s="5">
         <v>78</v>
@@ -5155,25 +4381,18 @@
         <v>-100</v>
       </c>
       <c r="K111" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L111" s="5">
-        <v>2</v>
-      </c>
-      <c r="M111" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M111" s="5"/>
       <c r="N111" s="5"/>
-      <c r="O111" s="5">
-        <v>0</v>
-      </c>
+      <c r="O111" s="5"/>
       <c r="P111" s="5"/>
       <c r="Q111" s="5"/>
-      <c r="R111" s="5"/>
-      <c r="S111" s="5"/>
-      <c r="T111" s="5"/>
-    </row>
-    <row r="112" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="112" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
         <v>111</v>
       </c>
@@ -5190,10 +4409,10 @@
         <v>6</v>
       </c>
       <c r="G112" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H112" s="5" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="I112" s="4">
         <v>133</v>
@@ -5202,19 +4421,13 @@
         <v>0</v>
       </c>
       <c r="K112" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L112" s="5">
-        <v>2</v>
-      </c>
-      <c r="M112" s="5">
-        <v>0</v>
-      </c>
-      <c r="O112" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
         <v>112</v>
       </c>
@@ -5231,10 +4444,10 @@
         <v>6</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H113" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="I113" s="4">
         <v>69</v>
@@ -5243,19 +4456,13 @@
         <v>0</v>
       </c>
       <c r="K113" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L113" s="5">
-        <v>1</v>
-      </c>
-      <c r="M113" s="5">
-        <v>0</v>
-      </c>
-      <c r="O113" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
         <v>113</v>
       </c>
@@ -5268,28 +4475,22 @@
         <v>6</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H114" s="9" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J114" s="5">
         <v>0</v>
       </c>
       <c r="K114" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L114" s="5">
-        <v>1</v>
-      </c>
-      <c r="M114" s="5">
-        <v>0</v>
-      </c>
-      <c r="O114" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
         <v>114</v>
       </c>
@@ -5306,10 +4507,10 @@
         <v>6</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H115" s="5" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I115" s="4">
         <v>45</v>
@@ -5318,19 +4519,13 @@
         <v>0</v>
       </c>
       <c r="K115" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L115" s="5">
-        <v>1</v>
-      </c>
-      <c r="M115" s="5">
-        <v>0</v>
-      </c>
-      <c r="O115" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="3">
         <v>115</v>
       </c>
@@ -5347,10 +4542,10 @@
         <v>6</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H116" s="5" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="I116" s="4">
         <v>175</v>
@@ -5362,16 +4557,10 @@
         <v>2</v>
       </c>
       <c r="L116" s="5">
-        <v>2</v>
-      </c>
-      <c r="M116" s="5">
-        <v>0</v>
-      </c>
-      <c r="O116" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
         <v>116</v>
       </c>
@@ -5388,10 +4577,10 @@
         <v>6</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="I117" s="4">
         <f>60*4+46</f>
@@ -5404,16 +4593,10 @@
         <v>2</v>
       </c>
       <c r="L117" s="5">
-        <v>2</v>
-      </c>
-      <c r="M117" s="5">
-        <v>0</v>
-      </c>
-      <c r="O117" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
         <v>117</v>
       </c>
@@ -5430,10 +4613,10 @@
         <v>6</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H118" s="5" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I118" s="4">
         <f>6*60+58</f>
@@ -5446,16 +4629,10 @@
         <v>2</v>
       </c>
       <c r="L118" s="5">
-        <v>2</v>
-      </c>
-      <c r="M118" s="5">
-        <v>0</v>
-      </c>
-      <c r="O118" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
         <v>118</v>
       </c>
@@ -5472,10 +4649,10 @@
         <v>3</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H119" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="I119" s="5">
         <v>223</v>
@@ -5484,25 +4661,18 @@
         <v>-100</v>
       </c>
       <c r="K119" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L119" s="5">
-        <v>2</v>
-      </c>
-      <c r="M119" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M119" s="5"/>
       <c r="N119" s="5"/>
-      <c r="O119" s="5">
-        <v>0</v>
-      </c>
+      <c r="O119" s="5"/>
       <c r="P119" s="5"/>
       <c r="Q119" s="5"/>
-      <c r="R119" s="5"/>
-      <c r="S119" s="5"/>
-      <c r="T119" s="5"/>
-    </row>
-    <row r="120" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="120" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
         <v>119</v>
       </c>
@@ -5519,10 +4689,10 @@
         <v>3</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="I120" s="5">
         <v>53</v>
@@ -5531,25 +4701,18 @@
         <v>100</v>
       </c>
       <c r="K120" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L120" s="5">
-        <v>1</v>
-      </c>
-      <c r="M120" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M120" s="5"/>
       <c r="N120" s="5"/>
-      <c r="O120" s="5">
-        <v>0</v>
-      </c>
+      <c r="O120" s="5"/>
       <c r="P120" s="5"/>
       <c r="Q120" s="5"/>
-      <c r="R120" s="5"/>
-      <c r="S120" s="5"/>
-      <c r="T120" s="5"/>
-    </row>
-    <row r="121" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="121" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
         <v>120</v>
       </c>
@@ -5566,10 +4729,10 @@
         <v>3</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H121" s="5" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I121" s="5">
         <v>90</v>
@@ -5578,25 +4741,18 @@
         <v>-100</v>
       </c>
       <c r="K121" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L121" s="5">
-        <v>1</v>
-      </c>
-      <c r="M121" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M121" s="5"/>
       <c r="N121" s="5"/>
-      <c r="O121" s="5">
-        <v>0</v>
-      </c>
+      <c r="O121" s="5"/>
       <c r="P121" s="5"/>
       <c r="Q121" s="5"/>
-      <c r="R121" s="5"/>
-      <c r="S121" s="5"/>
-      <c r="T121" s="5"/>
-    </row>
-    <row r="122" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="122" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="3">
         <v>121</v>
       </c>
@@ -5613,10 +4769,10 @@
         <v>6</v>
       </c>
       <c r="G122" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="I122" s="5">
         <v>49</v>
@@ -5628,16 +4784,10 @@
         <v>2</v>
       </c>
       <c r="L122" s="5">
-        <v>2</v>
-      </c>
-      <c r="M122" s="5">
-        <v>0</v>
-      </c>
-      <c r="O122" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="3">
         <v>122</v>
       </c>
@@ -5654,10 +4804,10 @@
         <v>6</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H123" s="5" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I123" s="5">
         <v>270</v>
@@ -5669,16 +4819,10 @@
         <v>2</v>
       </c>
       <c r="L123" s="5">
-        <v>2</v>
-      </c>
-      <c r="M123" s="5">
-        <v>0</v>
-      </c>
-      <c r="O123" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="3">
         <v>123</v>
       </c>
@@ -5695,10 +4839,10 @@
         <v>6</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H124" s="5" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="I124" s="5">
         <v>67</v>
@@ -5710,17 +4854,10 @@
         <v>1</v>
       </c>
       <c r="L124" s="5">
-        <v>1</v>
-      </c>
-      <c r="M124" s="5"/>
-      <c r="N124" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="O124" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="3">
         <v>124</v>
       </c>
@@ -5733,25 +4870,19 @@
         <v>3</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J125" s="5">
         <v>100</v>
       </c>
       <c r="K125" s="5">
-        <v>2</v>
-      </c>
-      <c r="L125" s="5">
-        <v>1</v>
-      </c>
-      <c r="M125" s="5">
-        <v>0</v>
-      </c>
-      <c r="O125" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="L125" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="3">
         <v>125</v>
       </c>
@@ -5768,10 +4899,10 @@
         <v>3</v>
       </c>
       <c r="G126" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H126" s="5" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I126" s="5">
         <v>194</v>
@@ -5783,22 +4914,15 @@
         <v>2</v>
       </c>
       <c r="L126" s="5">
-        <v>2</v>
-      </c>
-      <c r="M126" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M126" s="5"/>
       <c r="N126" s="5"/>
-      <c r="O126" s="5">
-        <v>0</v>
-      </c>
+      <c r="O126" s="5"/>
       <c r="P126" s="5"/>
       <c r="Q126" s="5"/>
-      <c r="R126" s="5"/>
-      <c r="S126" s="5"/>
-      <c r="T126" s="5"/>
-    </row>
-    <row r="127" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="127" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="3">
         <v>126</v>
       </c>
@@ -5811,19 +4935,16 @@
         <v>3</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J127" s="5">
         <v>-100</v>
       </c>
       <c r="K127" s="5">
-        <v>1</v>
-      </c>
-      <c r="L127" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="3">
         <v>127</v>
       </c>
@@ -5840,10 +4961,10 @@
         <v>3</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H128" s="5" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="I128" s="5">
         <v>290</v>
@@ -5855,22 +4976,15 @@
         <v>2</v>
       </c>
       <c r="L128" s="5">
-        <v>2</v>
-      </c>
-      <c r="M128" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M128" s="5"/>
       <c r="N128" s="5"/>
-      <c r="O128" s="5">
-        <v>0</v>
-      </c>
+      <c r="O128" s="5"/>
       <c r="P128" s="5"/>
       <c r="Q128" s="5"/>
-      <c r="R128" s="5"/>
-      <c r="S128" s="5"/>
-      <c r="T128" s="5"/>
-    </row>
-    <row r="129" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="129" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="3">
         <v>128</v>
       </c>
@@ -5883,7 +4997,7 @@
         <v>3</v>
       </c>
       <c r="G129" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J129" s="5">
         <v>100</v>
@@ -5891,17 +5005,11 @@
       <c r="K129" s="5">
         <v>1</v>
       </c>
-      <c r="L129" s="5">
-        <v>1</v>
-      </c>
-      <c r="M129" s="5">
-        <v>0</v>
-      </c>
-      <c r="O129" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L129" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="3">
         <v>129</v>
       </c>
@@ -5918,10 +5026,10 @@
         <v>3</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H130" s="5" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="I130" s="5">
         <v>157</v>
@@ -5933,22 +5041,15 @@
         <v>1</v>
       </c>
       <c r="L130" s="5">
-        <v>1</v>
-      </c>
-      <c r="M130" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M130" s="5"/>
       <c r="N130" s="5"/>
-      <c r="O130" s="5">
-        <v>0</v>
-      </c>
+      <c r="O130" s="5"/>
       <c r="P130" s="5"/>
       <c r="Q130" s="5"/>
-      <c r="R130" s="5"/>
-      <c r="S130" s="5"/>
-      <c r="T130" s="5"/>
-    </row>
-    <row r="131" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="131" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="3">
         <v>130</v>
       </c>
@@ -5965,10 +5066,10 @@
         <v>3</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H131" s="5" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I131" s="5">
         <v>183</v>
@@ -5977,25 +5078,18 @@
         <v>100</v>
       </c>
       <c r="K131" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L131" s="5">
-        <v>2</v>
-      </c>
-      <c r="M131" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M131" s="5"/>
       <c r="N131" s="5"/>
-      <c r="O131" s="5">
-        <v>0</v>
-      </c>
+      <c r="O131" s="5"/>
       <c r="P131" s="5"/>
       <c r="Q131" s="5"/>
-      <c r="R131" s="5"/>
-      <c r="S131" s="5"/>
-      <c r="T131" s="5"/>
-    </row>
-    <row r="132" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="132" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="3">
         <v>131</v>
       </c>
@@ -6012,10 +5106,10 @@
         <v>6</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H132" s="4" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I132" s="4">
         <v>59</v>
@@ -6026,14 +5120,11 @@
       <c r="K132" s="5">
         <v>1</v>
       </c>
-      <c r="L132" s="5">
-        <v>1</v>
-      </c>
-      <c r="O132" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L132" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="3">
         <v>132</v>
       </c>
@@ -6046,7 +5137,7 @@
         <v>6</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J133" s="5">
         <v>0</v>
@@ -6055,13 +5146,10 @@
         <v>1</v>
       </c>
       <c r="L133" s="5">
-        <v>1</v>
-      </c>
-      <c r="O133" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="3">
         <v>133</v>
       </c>
@@ -6078,10 +5166,10 @@
         <v>3</v>
       </c>
       <c r="G134" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H134" s="5" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I134" s="5">
         <v>159</v>
@@ -6093,22 +5181,15 @@
         <v>2</v>
       </c>
       <c r="L134" s="5">
-        <v>2</v>
-      </c>
-      <c r="M134" s="5">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M134" s="5"/>
       <c r="N134" s="5"/>
-      <c r="O134" s="5">
-        <v>0</v>
-      </c>
+      <c r="O134" s="5"/>
       <c r="P134" s="5"/>
       <c r="Q134" s="5"/>
-      <c r="R134" s="5"/>
-      <c r="S134" s="5"/>
-      <c r="T134" s="5"/>
-    </row>
-    <row r="135" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="135" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="3">
         <v>134</v>
       </c>
@@ -6125,10 +5206,10 @@
         <v>3</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H135" s="5" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="I135" s="5">
         <v>124</v>
@@ -6139,21 +5220,14 @@
       <c r="K135" s="5">
         <v>1</v>
       </c>
-      <c r="L135" s="5">
-        <v>1</v>
-      </c>
-      <c r="M135" s="5">
-        <v>0</v>
-      </c>
+      <c r="L135" s="5"/>
+      <c r="M135" s="5"/>
       <c r="N135" s="5"/>
       <c r="O135" s="5"/>
       <c r="P135" s="5"/>
       <c r="Q135" s="5"/>
-      <c r="R135" s="5"/>
-      <c r="S135" s="5"/>
-      <c r="T135" s="5"/>
-    </row>
-    <row r="136" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="136" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="3">
         <v>135</v>
       </c>
@@ -6166,22 +5240,16 @@
         <v>3</v>
       </c>
       <c r="G136" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J136" s="5">
         <v>100</v>
       </c>
       <c r="K136" s="5">
-        <v>2</v>
-      </c>
-      <c r="L136" s="5">
-        <v>1</v>
-      </c>
-      <c r="M136" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="3">
         <v>136</v>
       </c>
@@ -6194,16 +5262,16 @@
         <v>3</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J137" s="5">
         <v>0</v>
       </c>
-      <c r="O137" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L137" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="3">
         <v>137</v>
       </c>
@@ -6216,22 +5284,16 @@
         <v>3</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J138" s="5">
         <v>100</v>
       </c>
       <c r="K138" s="5">
-        <v>2</v>
-      </c>
-      <c r="L138" s="5">
-        <v>1</v>
-      </c>
-      <c r="M138" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="3">
         <v>138</v>
       </c>
@@ -6244,22 +5306,16 @@
         <v>3</v>
       </c>
       <c r="G139" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J139" s="5">
         <v>100</v>
       </c>
       <c r="K139" s="5">
-        <v>2</v>
-      </c>
-      <c r="L139" s="5">
-        <v>1</v>
-      </c>
-      <c r="M139" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="3">
         <v>139</v>
       </c>
@@ -6272,22 +5328,16 @@
         <v>3</v>
       </c>
       <c r="G140" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J140" s="5">
         <v>100</v>
       </c>
       <c r="K140" s="5">
-        <v>2</v>
-      </c>
-      <c r="L140" s="5">
-        <v>1</v>
-      </c>
-      <c r="M140" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="3">
         <v>140</v>
       </c>
@@ -6300,26 +5350,20 @@
         <v>3</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H141" s="5"/>
       <c r="J141" s="5">
         <v>100</v>
       </c>
       <c r="K141" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L141" s="5">
-        <v>1</v>
-      </c>
-      <c r="M141" s="5">
-        <v>0</v>
-      </c>
-      <c r="O141" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="3">
         <v>141</v>
       </c>
@@ -6336,10 +5380,10 @@
         <v>3</v>
       </c>
       <c r="G142" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H142" s="4" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="I142" s="4">
         <v>27</v>
@@ -6351,16 +5395,10 @@
         <v>1</v>
       </c>
       <c r="L142" s="5">
-        <v>1</v>
-      </c>
-      <c r="M142" s="5">
-        <v>0</v>
-      </c>
-      <c r="O142" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="3">
         <v>142</v>
       </c>
@@ -6377,10 +5415,10 @@
         <v>3</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H143" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I143" s="4">
         <v>70</v>
@@ -6392,16 +5430,10 @@
         <v>2</v>
       </c>
       <c r="L143" s="5">
-        <v>2</v>
-      </c>
-      <c r="M143" s="5">
-        <v>0</v>
-      </c>
-      <c r="O143" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:20" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:17" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="3">
         <v>143</v>
       </c>
@@ -6418,10 +5450,10 @@
         <v>3</v>
       </c>
       <c r="G144" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H144" s="9" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="I144" s="4">
         <v>62</v>
@@ -6430,19 +5462,13 @@
         <v>0</v>
       </c>
       <c r="K144" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L144" s="5">
-        <v>2</v>
-      </c>
-      <c r="M144" s="5">
-        <v>0</v>
-      </c>
-      <c r="O144" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:15" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="3">
         <v>144</v>
       </c>
@@ -6459,10 +5485,10 @@
         <v>3</v>
       </c>
       <c r="G145" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H145" s="4" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="I145" s="4">
         <v>63</v>
@@ -6474,16 +5500,10 @@
         <v>1</v>
       </c>
       <c r="L145" s="5">
-        <v>1</v>
-      </c>
-      <c r="M145" s="5">
-        <v>0</v>
-      </c>
-      <c r="O145" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:15" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="3">
         <v>145</v>
       </c>
@@ -6496,25 +5516,19 @@
         <v>3</v>
       </c>
       <c r="G146" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J146" s="5">
         <v>100</v>
       </c>
       <c r="K146" s="5">
-        <v>2</v>
-      </c>
-      <c r="L146" s="5">
-        <v>1</v>
-      </c>
-      <c r="M146" s="5">
-        <v>0</v>
-      </c>
-      <c r="O146" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:15" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="L146" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="3">
         <v>146</v>
       </c>
@@ -6527,22 +5541,16 @@
         <v>3</v>
       </c>
       <c r="G147" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J147" s="5">
         <v>100</v>
       </c>
       <c r="K147" s="5">
-        <v>2</v>
-      </c>
-      <c r="L147" s="5">
-        <v>1</v>
-      </c>
-      <c r="M147" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:15" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="3">
         <v>147</v>
       </c>
@@ -6555,7 +5563,7 @@
         <v>3</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J148" s="5">
         <v>100</v>
@@ -6563,17 +5571,11 @@
       <c r="K148" s="5">
         <v>2</v>
       </c>
-      <c r="L148" s="5">
-        <v>2</v>
-      </c>
-      <c r="M148" s="4">
-        <v>0</v>
-      </c>
-      <c r="O148" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="1:15" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L148" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="3">
         <v>148</v>
       </c>
@@ -6590,10 +5592,10 @@
         <v>3</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H149" s="5" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="I149" s="4">
         <v>250</v>
@@ -6604,14 +5606,8 @@
       <c r="K149" s="5">
         <v>2</v>
       </c>
-      <c r="L149" s="5">
-        <v>2</v>
-      </c>
-      <c r="M149" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:15" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="150" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="3">
         <v>149</v>
       </c>
@@ -6628,10 +5624,10 @@
         <v>3</v>
       </c>
       <c r="G150" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H150" s="5" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I150" s="4">
         <v>120</v>
@@ -6640,19 +5636,13 @@
         <v>0</v>
       </c>
       <c r="K150" s="5">
-        <v>2</v>
-      </c>
-      <c r="L150" s="5">
-        <v>1</v>
-      </c>
-      <c r="M150" s="5">
-        <v>0</v>
-      </c>
-      <c r="O150" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:15" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="L150" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="3">
         <v>150</v>
       </c>
@@ -6669,10 +5659,10 @@
         <v>3</v>
       </c>
       <c r="G151" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H151" s="5" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="I151" s="4">
         <v>199</v>
@@ -6683,17 +5673,11 @@
       <c r="K151" s="5">
         <v>2</v>
       </c>
-      <c r="L151" s="5">
-        <v>2</v>
-      </c>
-      <c r="M151" s="5">
-        <v>0</v>
-      </c>
-      <c r="O151" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:15" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L151" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="3">
         <v>151</v>
       </c>
@@ -6706,7 +5690,7 @@
         <v>3</v>
       </c>
       <c r="G152" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J152" s="5">
         <v>0</v>
@@ -6714,14 +5698,8 @@
       <c r="K152" s="5">
         <v>2</v>
       </c>
-      <c r="L152" s="5">
-        <v>2</v>
-      </c>
-      <c r="M152" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:15" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="153" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="3">
         <v>152</v>
       </c>
@@ -6734,7 +5712,7 @@
         <v>3</v>
       </c>
       <c r="G153" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I153" s="5"/>
       <c r="J153" s="5">
@@ -6743,14 +5721,8 @@
       <c r="K153" s="5">
         <v>2</v>
       </c>
-      <c r="L153" s="5">
-        <v>2</v>
-      </c>
-      <c r="M153" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:15" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="154" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="3">
         <v>153</v>
       </c>
@@ -6763,7 +5735,7 @@
         <v>3</v>
       </c>
       <c r="G154" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J154" s="5">
         <v>0</v>
@@ -6771,14 +5743,8 @@
       <c r="K154" s="5">
         <v>2</v>
       </c>
-      <c r="L154" s="5">
-        <v>2</v>
-      </c>
-      <c r="M154" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:15" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="155" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="3">
         <v>154</v>
       </c>
@@ -6791,7 +5757,7 @@
         <v>3</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J155" s="5">
         <v>0</v>
@@ -6799,14 +5765,8 @@
       <c r="K155" s="5">
         <v>2</v>
       </c>
-      <c r="L155" s="5">
-        <v>2</v>
-      </c>
-      <c r="M155" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:15" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="156" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="3">
         <v>155</v>
       </c>
@@ -6823,10 +5783,10 @@
         <v>3</v>
       </c>
       <c r="G156" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H156" s="4" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="I156" s="4">
         <v>95</v>
@@ -6835,19 +5795,13 @@
         <v>0</v>
       </c>
       <c r="K156" s="5">
-        <v>1</v>
-      </c>
-      <c r="L156" s="5">
         <v>2</v>
       </c>
-      <c r="M156" s="5">
-        <v>0</v>
-      </c>
-      <c r="O156" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="1:15" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L156" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="3">
         <v>156</v>
       </c>
@@ -6864,10 +5818,10 @@
         <v>3</v>
       </c>
       <c r="G157" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H157" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I157" s="4">
         <v>45</v>
@@ -6878,17 +5832,11 @@
       <c r="K157" s="5">
         <v>2</v>
       </c>
-      <c r="L157" s="5">
-        <v>2</v>
-      </c>
-      <c r="M157" s="4">
-        <v>0</v>
-      </c>
-      <c r="O157" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="1:15" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L157" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="3">
         <v>157</v>
       </c>
@@ -6901,13 +5849,13 @@
         <v>3</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J158" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:15" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="3">
         <v>158</v>
       </c>
@@ -6920,22 +5868,16 @@
         <v>3</v>
       </c>
       <c r="G159" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J159" s="5">
         <v>0</v>
       </c>
       <c r="K159" s="5">
-        <v>2</v>
-      </c>
-      <c r="L159" s="5">
-        <v>1</v>
-      </c>
-      <c r="M159" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="1:15" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="3">
         <v>159</v>
       </c>
@@ -6952,10 +5894,10 @@
         <v>3</v>
       </c>
       <c r="G160" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H160" s="5" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="I160" s="4">
         <v>138</v>
@@ -6964,19 +5906,13 @@
         <v>0</v>
       </c>
       <c r="K160" s="5">
-        <v>2</v>
-      </c>
-      <c r="L160" s="5">
-        <v>1</v>
-      </c>
-      <c r="M160" s="5">
-        <v>0</v>
-      </c>
-      <c r="O160" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="1:15" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="L160" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="3">
         <v>160</v>
       </c>
@@ -6993,10 +5929,10 @@
         <v>3</v>
       </c>
       <c r="G161" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H161" s="10" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="I161" s="4">
         <v>446</v>
@@ -7008,16 +5944,10 @@
         <v>2</v>
       </c>
       <c r="L161" s="4">
-        <v>2</v>
-      </c>
-      <c r="M161" s="4">
-        <v>0</v>
-      </c>
-      <c r="O161" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="1:15" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="3">
         <v>161</v>
       </c>
@@ -7034,10 +5964,10 @@
         <v>3</v>
       </c>
       <c r="G162" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H162" s="5" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="I162" s="5">
         <v>78</v>
@@ -7049,16 +5979,10 @@
         <v>1</v>
       </c>
       <c r="L162" s="5">
-        <v>1</v>
-      </c>
-      <c r="M162" s="5">
-        <v>0</v>
-      </c>
-      <c r="O162" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="1:15" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="3">
         <v>162</v>
       </c>
@@ -7071,25 +5995,19 @@
         <v>3</v>
       </c>
       <c r="G163" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J163" s="5">
         <v>0</v>
       </c>
       <c r="K163" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L163" s="5">
-        <v>1</v>
-      </c>
-      <c r="M163" s="5">
-        <v>0</v>
-      </c>
-      <c r="O163" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" spans="1:15" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="3">
         <v>163</v>
       </c>
@@ -7106,10 +6024,10 @@
         <v>3</v>
       </c>
       <c r="G164" s="5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H164" s="5" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="I164" s="5">
         <v>38</v>
@@ -7118,30 +6036,24 @@
         <v>0</v>
       </c>
       <c r="K164" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L164" s="5">
-        <v>1</v>
-      </c>
-      <c r="M164" s="5">
-        <v>0</v>
-      </c>
-      <c r="O164" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="166" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="167" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="168" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="169" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="170" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="171" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="172" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="173" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="174" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="175" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="176" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="166" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="167" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="168" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="169" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="170" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="171" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="172" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="173" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="174" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="175" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="176" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -7960,7 +6872,7 @@
     <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="994" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A994" s="22" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="B994" s="22"/>
       <c r="C994" s="22"/>
@@ -7968,7 +6880,7 @@
     </row>
     <row r="995" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A995" s="23" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="B995" s="23"/>
       <c r="C995" s="23"/>
